--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125537917</v>
+        <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>96897</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,38 +1217,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476033</v>
+        <v>476029</v>
       </c>
       <c r="R6" t="n">
-        <v>6504400</v>
+        <v>6504350</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1280,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Barrnaturskog, ålder 150 år+</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,142 +1338,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>125537373</v>
-      </c>
-      <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Olofstorp, Olofstorp, Vg</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>476029</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6504350</v>
-      </c>
-      <c r="S7" t="n">
-        <v>25</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Karlsborg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Undenäs</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Boel Nilsson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Boel Nilsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125538341</v>
+        <v>125538448</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,40 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476033</v>
+        <v>476083</v>
       </c>
       <c r="R2" t="n">
-        <v>6504400</v>
+        <v>6504419</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -769,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
+          <t>Bohål i äldre tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125538448</v>
+        <v>125538341</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,35 +818,40 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476083</v>
+        <v>476033</v>
       </c>
       <c r="R3" t="n">
-        <v>6504419</v>
+        <v>6504400</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,12 +910,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Bohål i äldre tall</t>
+          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +942,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125536906</v>
+        <v>125537373</v>
       </c>
       <c r="B4" t="n">
-        <v>74964</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,38 +954,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476032</v>
+        <v>476029</v>
       </c>
       <c r="R4" t="n">
-        <v>6504355</v>
+        <v>6504350</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1017,7 +1036,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +1046,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Barrnaturskog, senvuxen 150 år+</t>
+          <t>Barrnaturskog, ålder 150 år+</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,21 +1062,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1074,10 +1078,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125538852</v>
+        <v>125536906</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
+        <v>74964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,52 +1090,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476162</v>
+        <v>476032</v>
       </c>
       <c r="R5" t="n">
-        <v>6504432</v>
+        <v>6504355</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1163,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1173,12 +1163,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
+          <t>Barrnaturskog, senvuxen 150 år+</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,6 +1179,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125537373</v>
+        <v>125538852</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,40 +1222,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476029</v>
+        <v>476162</v>
       </c>
       <c r="R6" t="n">
-        <v>6504350</v>
+        <v>6504432</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
+          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125538448</v>
+        <v>125536906</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476083</v>
+        <v>476032</v>
       </c>
       <c r="R2" t="n">
-        <v>6504419</v>
+        <v>6504355</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -764,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Bohål i äldre tall</t>
+          <t>Barrnaturskog, senvuxen 150 år+</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,6 +771,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,52 +802,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125538341</v>
+        <v>125538852</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -865,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476033</v>
+        <v>476162</v>
       </c>
       <c r="R3" t="n">
-        <v>6504400</v>
+        <v>6504432</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -900,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -910,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Stort antal utspridda i sluttningen, flertal torkade blomstänglar från i fjol. Barrnaturskog.</t>
+          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,15 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125537373</v>
+        <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,7 +958,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1001,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476029</v>
+        <v>476033</v>
       </c>
       <c r="R4" t="n">
-        <v>6504350</v>
+        <v>6504400</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1036,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1046,12 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
+          <t>Barrnaturskog, senvuxen. Ålder 150 år+</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1078,50 +1059,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125536906</v>
+        <v>125538448</v>
       </c>
       <c r="B5" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Olofstorp, Olofstorp, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476032</v>
+        <v>476083</v>
       </c>
       <c r="R5" t="n">
-        <v>6504355</v>
+        <v>6504419</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1153,7 +1143,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,12 +1153,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Barrnaturskog, senvuxen 150 år+</t>
+          <t>Bohål i äldre tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,21 +1169,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1210,47 +1185,47 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125538852</v>
+        <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1264,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476162</v>
+        <v>476029</v>
       </c>
       <c r="R6" t="n">
-        <v>6504432</v>
+        <v>6504350</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1299,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1309,12 +1284,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
+          <t>Barrnaturskog, ålder 150 år+</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125536906</v>
       </c>
       <c r="B2" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125536906</v>
       </c>
       <c r="B2" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>125538852</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>125538448</v>
       </c>
       <c r="B5" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>125537690</v>
       </c>
       <c r="B4" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>125537373</v>
       </c>
       <c r="B6" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>125536906</v>
       </c>
       <c r="B2" t="n">
-        <v>75007</v>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -802,27 +802,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125538852</v>
+        <v>125538448</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476162</v>
+        <v>476083</v>
       </c>
       <c r="R3" t="n">
-        <v>6504432</v>
+        <v>6504419</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
+          <t>Bohål i äldre tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,47 +928,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125537690</v>
+        <v>115532421</v>
       </c>
       <c r="B4" t="n">
-        <v>98343</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -978,14 +969,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Olofstorp, Olofstorp, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476033</v>
+        <v>476260</v>
       </c>
       <c r="R4" t="n">
-        <v>6504400</v>
+        <v>6504394</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,27 +1003,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Barrnaturskog, senvuxen. Ålder 150 år+</t>
+          <t>Rickhack på äldre tall, en av flera i närområdet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125538448</v>
+        <v>115532595</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,16 +1061,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1087,14 +1078,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1104,14 +1091,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Olofstorp, Olofstorp, Vg</t>
+          <t>Dalen, Dalen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476083</v>
+        <v>476210</v>
       </c>
       <c r="R5" t="n">
-        <v>6504419</v>
+        <v>6504435</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1138,27 +1125,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2024-03-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Bohål i äldre tall</t>
+          <t>Rickhack på äldre tall, en av flera i området.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,47 +1172,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125537373</v>
+        <v>125538852</v>
       </c>
       <c r="B6" t="n">
-        <v>98343</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1239,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476029</v>
+        <v>476162</v>
       </c>
       <c r="R6" t="n">
-        <v>6504350</v>
+        <v>6504432</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1274,7 +1256,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,12 +1266,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barrnaturskog, ålder 150 år+</t>
+          <t>Färska ringhack på tall med kådflöde. Barrnaturskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1313,6 +1295,409 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>103964460</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57144</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>476091</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6504140</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-09-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flög över hygget, landade i tall en kort stund innan flög vidare in i skogen</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125537373</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476029</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6504350</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Barrnaturskog, ålder 150 år+</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125537690</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Olofstorp, Olofstorp, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>476033</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6504400</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Barrnaturskog, senvuxen. Ålder 150 år+</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47703-2021 artfynd.xlsx
+++ b/artfynd/A 47703-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125536906</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -925,6 +935,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125538448</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115532421</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1169,6 +1189,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115532595</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1295,6 +1320,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125538852</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1436,6 +1466,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103964460</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1567,6 +1602,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125537373</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1698,8 +1738,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125537690</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>